--- a/data/stx_xlsx/LOGIa.ST.xlsx
+++ b/data/stx_xlsx/LOGIa.ST.xlsx
@@ -9099,9 +9099,7 @@
         <v>4.71</v>
       </c>
       <c r="F49" s="17"/>
-      <c r="G49" s="15">
-        <v>934.38</v>
-      </c>
+      <c r="G49" s="15"/>
       <c r="H49" s="16">
         <v>14.86</v>
       </c>
@@ -9129,9 +9127,18 @@
       <c r="P49" s="16">
         <v>3.87</v>
       </c>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="17"/>
+      <c r="Q49" s="16">
+        <f t="shared" ref="Q49:S49" si="1">SUM(Q50:Q51)</f>
+        <v>6.99</v>
+      </c>
+      <c r="R49" s="16">
+        <f t="shared" si="1"/>
+        <v>3.99</v>
+      </c>
+      <c r="S49" s="16">
+        <f t="shared" si="1"/>
+        <v>1.52</v>
+      </c>
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
